--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1185,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>2361.15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>205.37</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>2495.93</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>1210.28</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
+          <t>3 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
           <t>1 de 24</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>3 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
         <v>6827.71</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>5062.45</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>5000</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>1210.28</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>6681.43</v>
+        <v>12954.16</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2801.71</v>
+        <v>6373.14</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2388.29</v>
+        <v>-1183.14</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5398285163776493</v>
+        <v>1.227965317919075</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>205.37</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>963</v>
+        <v>757.63</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.2132606438213915</v>
       </c>
     </row>
     <row r="9">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4018.81</v>
+        <v>6514.74</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32537.19</v>
+        <v>30041.26</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.109935715067294</v>
+        <v>0.1782126053178685</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6681.43</v>
+        <v>12954.16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44915.45</v>
+        <v>38642.72</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1294929073230784</v>
+        <v>0.251064793065007</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-139.09</v>
+        <v>-203.91</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>5886.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-139.09</v>
+        <v>-203.91</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12954.16</v>
+        <v>12889.34</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2743,7 +2743,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2865,13 +2865,13 @@
         <v>199.5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-139.09</v>
+        <v>-203.91</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>338.59</v>
+        <v>403.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.6971929824561404</v>
+        <v>-1.022105263157895</v>
       </c>
     </row>
     <row r="6">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12954.16</v>
+        <v>12889.34</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38642.72</v>
+        <v>38707.54</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.251064793065007</v>
+        <v>0.2498085155536536</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1188,7 +1188,7 @@
         <v>2361.15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>205.37</v>
+        <v>595.65</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2495.93</v>
+        <v>4016.57</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>6827.71</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5062.45</v>
+        <v>6973.37</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>5000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12889.34</v>
+        <v>14800.26</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>205.37</v>
+        <v>595.65</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>757.63</v>
+        <v>367.35</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.2132606438213915</v>
+        <v>0.6185358255451713</v>
       </c>
     </row>
     <row r="9">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6514.74</v>
+        <v>8035.38</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>30041.26</v>
+        <v>28520.62</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1782126053178685</v>
+        <v>0.2198101542838385</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12889.34</v>
+        <v>14800.26</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38707.54</v>
+        <v>36796.62</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2498085155536536</v>
+        <v>0.2868440882471963</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1263.36</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1550.24</v>
+        <v>2813.6</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>14800.26</v>
+        <v>16063.62</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1263.36</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>407</v>
+        <v>-856.3599999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>3.104078624078624</v>
       </c>
     </row>
     <row r="12">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14800.26</v>
+        <v>16063.62</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>36796.62</v>
+        <v>35533.26</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2868440882471963</v>
+        <v>0.3113292896779805</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1185,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2361.15</v>
+        <v>4187.7</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>595.65</v>
+        <v>735.05</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1210.28</v>
+        <v>1774.58</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>6827.71</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6973.37</v>
+        <v>8939.32</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>5000</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1210.28</v>
+        <v>1774.58</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>16063.62</v>
+        <v>18593.87</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6373.14</v>
+        <v>8763.99</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1183.14</v>
+        <v>-3573.99</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.227965317919075</v>
+        <v>1.688630057803468</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>595.65</v>
+        <v>735.05</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>367.35</v>
+        <v>227.95</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6185358255451713</v>
+        <v>0.7632917964693665</v>
       </c>
     </row>
     <row r="9">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16063.62</v>
+        <v>18593.87</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>35533.26</v>
+        <v>33003.01</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3113292896779805</v>
+        <v>0.3603681075289823</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1263.36</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2813.6</v>
+        <v>1550.24</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18593.87</v>
+        <v>17330.51</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1263.36</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-856.3599999999999</v>
+        <v>407</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.104078624078624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18593.87</v>
+        <v>17330.51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33003.01</v>
+        <v>34266.37</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3603681075289823</v>
+        <v>0.3358829060981981</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>355.32</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>355.32</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>17330.51</v>
+        <v>17685.83</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>355.32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>407</v>
+        <v>51.68000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.873022113022113</v>
       </c>
     </row>
     <row r="12">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>17330.51</v>
+        <v>17685.83</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34266.37</v>
+        <v>33911.05</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3358829060981981</v>
+        <v>0.3427693690006062</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1029.61</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>3245.36</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1550.24</v>
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
+        <v>4672.8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>3656.3</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0</v>
@@ -2026,27 +2026,27 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
+          <t>4 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
           <t>3 de 24</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>0 de 24</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>1 de 24</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>1 de 24</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1550.24</v>
+        <v>5825.21</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>8329.1</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>17685.83</v>
+        <v>30289.9</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2741,7 +2741,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8763.99</v>
+        <v>13436.79</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-3573.99</v>
+        <v>-8246.790000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.688630057803468</v>
+        <v>2.588976878612717</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>735.05</v>
+        <v>5420.96</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>227.95</v>
+        <v>-4457.96</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7632917964693665</v>
+        <v>5.629241952232606</v>
       </c>
     </row>
     <row r="9">
@@ -3057,13 +3057,13 @@
         <v>1467</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>3245.36</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1467</v>
+        <v>-1778.36</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>2.212242672119973</v>
       </c>
     </row>
     <row r="14">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>17685.83</v>
+        <v>30289.9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33911.05</v>
+        <v>21306.98</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3427693690006062</v>
+        <v>0.587049061881261</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -765,10 +765,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1846.35</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>325.23</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>782.5599999999999</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>1284.32</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4187.7</v>
+        <v>4283.4</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>735.05</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4016.57</v>
+        <v>8386.6</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
+          <t>5 de 24</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
           <t>4 de 24</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>3 de 24</t>
-        </is>
-      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>0 de 24</t>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>3 de 24</t>
+          <t>4 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
         <v>4847.61</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>4238.46</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>4000</v>
@@ -2431,7 +2431,7 @@
         <v>6827.71</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8939.32</v>
+        <v>13405.05</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>5000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>30289.9</v>
+        <v>38994.09</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13436.79</v>
+        <v>15378.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-8246.790000000001</v>
+        <v>-10188.84</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.588976878612717</v>
+        <v>2.963167630057804</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5420.96</v>
+        <v>5746.19</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-4457.96</v>
+        <v>-4783.19</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5.629241952232606</v>
+        <v>5.966967808930425</v>
       </c>
     </row>
     <row r="9">
@@ -3057,13 +3057,13 @@
         <v>1467</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3245.36</v>
+        <v>4027.92</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-1778.36</v>
+        <v>-2560.92</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.212242672119973</v>
+        <v>2.745685071574642</v>
       </c>
     </row>
     <row r="14">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8035.38</v>
+        <v>13689.73</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28520.62</v>
+        <v>22866.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2198101542838385</v>
+        <v>0.3744865411970675</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>30289.9</v>
+        <v>38994.09</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21306.98</v>
+        <v>12602.79</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.587049061881261</v>
+        <v>0.755745114820896</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>2001.54</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>2105.78</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>671.24</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>3245.36</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1550.24</v>
+        <v>4218.96</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>5837.83</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>4 de 24</t>
+          <t>7 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>8279.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>7985.72</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6000</v>
@@ -2485,7 +2485,7 @@
         <v>5886.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-203.91</v>
+        <v>1901.87</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5000</v>
@@ -2512,7 +2512,7 @@
         <v>3252.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5825.21</v>
+        <v>9198.93</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>8329.1</v>
+        <v>14166.93</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>38994.09</v>
+        <v>58297.14</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2841,13 +2841,13 @@
         <v>3732</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>6017.94</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3732</v>
+        <v>-2285.94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1.612524115755627</v>
       </c>
     </row>
     <row r="5">
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>355.32</v>
+        <v>1026.56</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>51.68000000000001</v>
+        <v>-619.5599999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.873022113022113</v>
+        <v>2.522260442260442</v>
       </c>
     </row>
     <row r="12">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13689.73</v>
+        <v>26303.6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22866.27</v>
+        <v>10252.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3744865411970675</v>
+        <v>0.7195426195426196</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>38994.09</v>
+        <v>58297.14</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12602.79</v>
+        <v>-6700.259999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.755745114820896</v>
+        <v>1.129857851870113</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1148.4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>273.19</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>2162.98</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>652.34</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>9360.940000000001</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>5 de 24</t>
+          <t>6 de 24</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>4 de 24</t>
+          <t>6 de 24</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>7 de 24</t>
+          <t>9 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>8279.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7985.72</v>
+        <v>9407.309999999999</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6000</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2801.71</v>
+        <v>4964.69</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>10013.28</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>43619.47</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>58297.14</v>
+        <v>71894.99000000001</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2913,13 +2913,13 @@
         <v>5190</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15378.84</v>
+        <v>16527.24</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-10188.84</v>
+        <v>-11337.24</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.963167630057804</v>
+        <v>3.184439306358382</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>963</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5746.19</v>
+        <v>6671.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-4783.19</v>
+        <v>-5708.72</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5.966967808930425</v>
+        <v>6.928058151609553</v>
       </c>
     </row>
     <row r="9">
@@ -3081,13 +3081,13 @@
         <v>36556</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26303.6</v>
+        <v>37827.52</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10252.4</v>
+        <v>-1271.519999999997</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7195426195426196</v>
+        <v>1.034782798993325</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51596.88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58297.14</v>
+        <v>71894.98999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-6700.259999999999</v>
+        <v>-20298.11</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.129857851870113</v>
+        <v>1.39339801166272</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -765,10 +765,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1846.35</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>325.23</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>782.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1284.32</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1148.4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>273.19</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2001.54</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2468.57</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>355.32</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4283.4</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>735.05</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8386.6</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-203.91</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2105.78</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1488,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1029.61</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>671.24</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3245.36</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4218.96</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2801.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2162.98</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>652.34</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9360.940000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1774.58</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4672.8</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3656.3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5837.83</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>6 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>6 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>9 de 24</t>
+          <t>0 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2096,10 +2096,10 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>3902.2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3902.2</v>
+        <v>4847.61</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4847.61</v>
+        <v>4238.46</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4238.46</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>4000</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>1812.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1812.75</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -2233,16 +2233,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-37.78</v>
+        <v>11690.15</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11690.15</v>
+        <v>8279.9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8279.9</v>
+        <v>9407.309999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>9407.309999999999</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6000</v>
@@ -2266,10 +2266,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2468.57</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2468.57</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>3502.7</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3502.7</v>
+        <v>2393.76</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2393.76</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2368,16 +2368,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>2964.44</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2964.44</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>355.32</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>355.32</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2000</v>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2916.85</v>
+        <v>1133.57</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1133.57</v>
+        <v>6827.71</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6827.71</v>
+        <v>13405.05</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>13405.05</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>5000</v>
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>125.19</v>
+        <v>4755.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4755.17</v>
+        <v>5886.02</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5886.02</v>
+        <v>2130.47</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1901.87</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5000</v>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7791.96</v>
+        <v>8281.98</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8281.98</v>
+        <v>3252.74</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3252.74</v>
+        <v>9198.93</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>9198.93</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2557,16 +2557,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1047.1</v>
+        <v>1390.37</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1390.37</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>4964.69</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4964.69</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1500</v>
@@ -2587,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>12131.73</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12131.73</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>-10114.14</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-10114.14</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>10013.28</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>10013.28</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2665,16 +2665,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>6488.12</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6488.12</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1090.65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1774.58</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3000</v>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>11134.19</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11134.19</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>14166.93</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>14166.93</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>6000</v>
@@ -2709,16 +2709,16 @@
     </row>
     <row r="23">
       <c r="C23" s="6" t="n">
-        <v>11843.32</v>
+        <v>46941.5</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>46941.5</v>
+        <v>43619.47</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>43619.47</v>
+        <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>71894.99000000001</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1572.87</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>9198.93</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>1572.87</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>1572.87</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>45500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="8">
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="13">
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18">
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="19">
@@ -2623,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="20">
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="23">
@@ -2721,7 +2721,7 @@
         <v>1572.87</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>45500</v>
+        <v>51500</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>-228.6</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>2130.47</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>-228.6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1572.87</v>
+        <v>1344.27</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2741,8 +2741,8 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2183</v>
+        <v>3183</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2183</v>
+        <v>3183</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -2841,13 +2841,13 @@
         <v>3732</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6017.94</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-2285.94</v>
+        <v>3732</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.612524115755627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2865,13 +2865,13 @@
         <v>199.5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-203.91</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>403.41</v>
+        <v>199.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-1.022105263157895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2910,16 +2910,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5190</v>
+        <v>700</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16527.24</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-11337.24</v>
+        <v>700</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.184439306358382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>963</v>
+        <v>300</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6671.72</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-5708.72</v>
+        <v>300</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>6.928058151609553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1026.56</v>
+        <v>1572.87</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-619.5599999999999</v>
+        <v>-1165.87</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.522260442260442</v>
+        <v>3.864545454545454</v>
       </c>
     </row>
     <row r="12">
@@ -3057,13 +3057,13 @@
         <v>1467</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4027.92</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-2560.92</v>
+        <v>1467</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.745685071574642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3078,16 +3078,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>36556</v>
+        <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>37827.52</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-1271.519999999997</v>
+        <v>40549.17</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.034782798993325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3105,13 +3105,13 @@
         <v>199.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>-228.6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>199.8</v>
+        <v>428.4</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>-1.144144144144144</v>
       </c>
     </row>
     <row r="16">
@@ -3121,16 +3121,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>51596.88</v>
+        <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>71894.98999999999</v>
+        <v>1344.27</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-20298.11</v>
+        <v>50092.78</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.39339801166272</v>
+        <v>0.02613427480775044</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>-376.2</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>1090.65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>-376.2</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1344.27</v>
+        <v>968.0699999999999</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -2743,7 +2743,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2913,13 +2913,13 @@
         <v>700</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>-376.2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>700</v>
+        <v>1076.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>-0.5374285714285714</v>
       </c>
     </row>
     <row r="8">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1344.27</v>
+        <v>968.0699999999998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50092.78</v>
+        <v>50468.98</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02613427480775044</v>
+        <v>0.01882048056799525</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>228.61</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
         <v>13405.05</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>228.61</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>968.0699999999999</v>
+        <v>1196.68</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -2742,7 +2742,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2937,13 +2937,13 @@
         <v>300</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>228.61</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>300</v>
+        <v>71.38999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.7620333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>968.0699999999998</v>
+        <v>1196.68</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50468.98</v>
+        <v>50240.37</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.01882048056799525</v>
+        <v>0.02326494229354133</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>327.77</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>8639.49</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>2227.16</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2242,7 +2242,7 @@
         <v>9407.309999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>327.77</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6000</v>
@@ -2512,7 +2512,7 @@
         <v>9198.93</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1572.87</v>
+        <v>10212.36</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2566,7 +2566,7 @@
         <v>4964.69</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>2227.16</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1196.68</v>
+        <v>12391.1</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -2741,7 +2741,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3057,13 +3057,13 @@
         <v>1467</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>327.77</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1467</v>
+        <v>1139.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.2234287661895024</v>
       </c>
     </row>
     <row r="14">
@@ -3081,13 +3081,13 @@
         <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>10866.65</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>40549.17</v>
+        <v>29682.52</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>0.2679869896227222</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1196.68</v>
+        <v>12391.1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50240.37</v>
+        <v>39045.95</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02326494229354133</v>
+        <v>0.2408983407874285</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>270.91</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>3 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
         <v>14166.93</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>270.91</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>7000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12391.1</v>
+        <v>12662.01</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -3081,13 +3081,13 @@
         <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10866.65</v>
+        <v>11137.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29682.52</v>
+        <v>29411.61</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2679869896227222</v>
+        <v>0.2746680141665045</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12391.1</v>
+        <v>12662.01</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39045.95</v>
+        <v>38775.04</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2408983407874285</v>
+        <v>0.2461651669370619</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>1006.25</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>3 de 24</t>
+          <t>4 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
         <v>13405.05</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>228.61</v>
+        <v>1234.86</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12662.01</v>
+        <v>13668.26</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -3081,13 +3081,13 @@
         <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11137.56</v>
+        <v>12143.81</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29411.61</v>
+        <v>28405.36</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2746680141665045</v>
+        <v>0.2994835652616317</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12662.01</v>
+        <v>13668.26</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38775.04</v>
+        <v>37768.79</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2461651669370619</v>
+        <v>0.2657279140230631</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
+        <v>-160.88</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>-151.74</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>14166.93</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>270.91</v>
+        <v>-41.71</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>7000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>13668.26</v>
+        <v>13355.64</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -2742,8 +2742,8 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2913,13 +2913,13 @@
         <v>700</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-376.2</v>
+        <v>-537.08</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1076.2</v>
+        <v>1237.08</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0.5374285714285714</v>
+        <v>-0.767257142857143</v>
       </c>
     </row>
     <row r="8">
@@ -2937,13 +2937,13 @@
         <v>300</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>228.61</v>
+        <v>76.87</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>71.38999999999999</v>
+        <v>223.13</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.7620333333333333</v>
+        <v>0.2562333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13668.26</v>
+        <v>13355.64</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37768.79</v>
+        <v>38081.41</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2657279140230631</v>
+        <v>0.2596501937805531</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>327.77</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1006.25</v>
+        <v>4024.99</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1572.87</v>
+        <v>1590.78</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8639.49</v>
+        <v>10651.98</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>1 de 24</t>
+          <t>2 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>9407.309999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>327.77</v>
+        <v>345.68</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6000</v>
@@ -2431,7 +2431,7 @@
         <v>13405.05</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1234.86</v>
+        <v>4253.6</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6000</v>
@@ -2512,7 +2512,7 @@
         <v>9198.93</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>10212.36</v>
+        <v>12242.76</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>13355.64</v>
+        <v>18422.69</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1572.87</v>
+        <v>1608.69</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1165.87</v>
+        <v>-1201.69</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.864545454545454</v>
+        <v>3.952555282555283</v>
       </c>
     </row>
     <row r="12">
@@ -3081,13 +3081,13 @@
         <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12143.81</v>
+        <v>17175.04</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28405.36</v>
+        <v>23374.13</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2994835652616317</v>
+        <v>0.4235608275089232</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13355.64</v>
+        <v>18422.69</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38081.41</v>
+        <v>33014.36</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2596501937805531</v>
+        <v>0.3581599255789358</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -2674,7 +2674,7 @@
         <v>1090.65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-376.2</v>
+        <v>-353.44</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18422.69</v>
+        <v>18445.45</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -2743,7 +2743,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2841,13 +2841,13 @@
         <v>3732</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>22.76</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3732</v>
+        <v>3709.24</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.00609860664523044</v>
       </c>
     </row>
     <row r="5">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18422.69</v>
+        <v>18445.45</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33014.36</v>
+        <v>32991.6</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3581599255789358</v>
+        <v>0.3586024081863171</v>
       </c>
     </row>
   </sheetData>

--- a/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
+++ b/data/HIDALGO HIDALGO PEDRO GUSTAVO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1134.21</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>-228.6</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>270.91</v>
+        <v>8309.92</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2 de 24</t>
+          <t>4 de 24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>4 de 24</t>
+          <t>5 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>2130.47</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-228.6</v>
+        <v>905.61</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6000</v>
@@ -2566,7 +2566,7 @@
         <v>4964.69</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2227.16</v>
+        <v>2245.07</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2000</v>
@@ -2701,7 +2701,7 @@
         <v>14166.93</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-41.71</v>
+        <v>8015.21</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>7000</v>
@@ -2718,7 +2718,7 @@
         <v>71439.66</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18445.45</v>
+        <v>27654.49</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>51500</v>
@@ -3009,13 +3009,13 @@
         <v>407</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1608.69</v>
+        <v>1644.51</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1201.69</v>
+        <v>-1237.51</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.952555282555283</v>
+        <v>4.040565110565111</v>
       </c>
     </row>
     <row r="12">
@@ -3081,13 +3081,13 @@
         <v>40549.17</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>17175.04</v>
+        <v>26348.26</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23374.13</v>
+        <v>14200.91</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.4235608275089232</v>
+        <v>0.649785433339326</v>
       </c>
     </row>
     <row r="15">
@@ -3124,13 +3124,13 @@
         <v>51437.05</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18445.45</v>
+        <v>27654.49</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32991.6</v>
+        <v>23782.56</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3586024081863171</v>
+        <v>0.5376375589191059</v>
       </c>
     </row>
   </sheetData>
